--- a/data/pricing_plan.xlsx
+++ b/data/pricing_plan.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yangfan/project/lobeai/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C87AD5A-FE85-FE45-8601-44275C6EEAF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F24A4697-89FD-BC4D-A02F-54F5913018C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>model</t>
   </si>
@@ -37,12 +37,6 @@
     <t>enterprise</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>anthropic/claude-haiku-4.5</t>
   </si>
   <si>
@@ -68,6 +62,24 @@
   </si>
   <si>
     <t>openai/o3</t>
+  </si>
+  <si>
+    <t>google/gemini-3.1-pro-preview</t>
+  </si>
+  <si>
+    <t>google/gemini-3-flash-preview</t>
+  </si>
+  <si>
+    <t>openai/gpt-5.3-codex</t>
+  </si>
+  <si>
+    <t>openai/gpt-5.4</t>
+  </si>
+  <si>
+    <t>x-ai/grok-4.1</t>
+  </si>
+  <si>
+    <t>x-ai/grok-4.20-beta</t>
   </si>
 </sst>
 </file>
@@ -110,8 +122,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -451,187 +469,286 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1">
+        <v>1</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" t="s">
+      <c r="B9" s="1">
+        <v>1</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" t="s">
+      <c r="B10" s="1">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2">
+        <v>1</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" t="s">
+      <c r="B11" s="1">
+        <v>1</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5</v>
+      <c r="B12" s="1">
+        <v>1</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="1">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="1">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0</v>
+      </c>
+      <c r="E14" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="1">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1">
+        <v>1</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
+      <c r="E15" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="1">
+        <v>1</v>
+      </c>
+      <c r="C16" s="1">
+        <v>0</v>
+      </c>
+      <c r="D16" s="1">
+        <v>0</v>
+      </c>
+      <c r="E16" s="1">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:E1 A2:E10" numberStoredAsText="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
--- a/data/pricing_plan.xlsx
+++ b/data/pricing_plan.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yangfan/project/lobeai/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F24A4697-89FD-BC4D-A02F-54F5913018C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98391938-93FA-4A4F-9B7C-FB055572DF65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="pricing_db" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>model</t>
   </si>
@@ -46,24 +59,6 @@
     <t>anthropic/claude-sonnet-4.6</t>
   </si>
   <si>
-    <t>google/gemini-2.0-flash-001</t>
-  </si>
-  <si>
-    <t>google/gemini-2.5-flash</t>
-  </si>
-  <si>
-    <t>openai/gpt-4.1</t>
-  </si>
-  <si>
-    <t>openai/gpt-4.1-mini</t>
-  </si>
-  <si>
-    <t>openai/gpt-5.1</t>
-  </si>
-  <si>
-    <t>openai/o3</t>
-  </si>
-  <si>
     <t>google/gemini-3.1-pro-preview</t>
   </si>
   <si>
@@ -76,10 +71,25 @@
     <t>openai/gpt-5.4</t>
   </si>
   <si>
-    <t>x-ai/grok-4.1</t>
-  </si>
-  <si>
     <t>x-ai/grok-4.20-beta</t>
+  </si>
+  <si>
+    <t>openai/gpt-5.4-mini</t>
+  </si>
+  <si>
+    <t>openai/gpt-5.4-nano</t>
+  </si>
+  <si>
+    <t>x-ai/grok-4.1-fast</t>
+  </si>
+  <si>
+    <t>x-ai/grok-4</t>
+  </si>
+  <si>
+    <t>google/gemini-3.1-flash-lite-preview</t>
+  </si>
+  <si>
+    <t>google/gemini-3-pro-preview</t>
   </si>
 </sst>
 </file>
@@ -127,8 +137,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -469,13 +479,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:XFD15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="41" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="10.83203125" style="1"/>
+    <col min="9" max="9" width="33.1640625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:7 16384:16384">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -492,258 +504,249 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:7 16384:16384">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
       </c>
-      <c r="C2" s="2">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:7 16384:16384">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="1">
         <v>0</v>
       </c>
       <c r="D3" s="1">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:7 16384:16384">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
       </c>
-      <c r="C4" s="2">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="C4" s="1">
+        <v>0</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7 16384:16384">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="C5" s="2">
-        <v>1</v>
-      </c>
-      <c r="D5" s="2">
-        <v>1</v>
-      </c>
-      <c r="E5" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+      <c r="XFD5">
+        <f>SUM(B5:XFC5)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7 16384:16384">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
       </c>
-      <c r="C6" s="2">
-        <v>0</v>
-      </c>
-      <c r="D6" s="2">
-        <v>1</v>
-      </c>
-      <c r="E6" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="C6" s="1">
+        <v>0</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7 16384:16384">
       <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7 16384:16384">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7 16384:16384">
+      <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="1">
-        <v>1</v>
-      </c>
-      <c r="C7" s="1">
-        <v>0</v>
-      </c>
-      <c r="D7" s="1">
-        <v>1</v>
-      </c>
-      <c r="E7" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="1" t="s">
+      <c r="B9" s="1">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7 16384:16384">
+      <c r="A10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="1">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7 16384:16384">
+      <c r="A11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7 16384:16384">
+      <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7 16384:16384">
+      <c r="A13" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="1">
-        <v>1</v>
-      </c>
-      <c r="C8" s="1">
-        <v>1</v>
-      </c>
-      <c r="D8" s="1">
-        <v>1</v>
-      </c>
-      <c r="E8" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="1">
-        <v>1</v>
-      </c>
-      <c r="C9" s="2">
-        <v>0</v>
-      </c>
-      <c r="D9" s="2">
-        <v>1</v>
-      </c>
-      <c r="E9" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="1">
-        <v>1</v>
-      </c>
-      <c r="C10" s="2">
-        <v>1</v>
-      </c>
-      <c r="D10" s="2">
-        <v>1</v>
-      </c>
-      <c r="E10" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="1" t="s">
+      <c r="B13" s="1">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7 16384:16384">
+      <c r="A14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="1">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7 16384:16384">
+      <c r="A15" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="1">
-        <v>1</v>
-      </c>
-      <c r="C11" s="2">
-        <v>0</v>
-      </c>
-      <c r="D11" s="1">
-        <v>1</v>
-      </c>
-      <c r="E11" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="1">
-        <v>1</v>
-      </c>
-      <c r="C12" s="2">
-        <v>0</v>
-      </c>
-      <c r="D12" s="1">
-        <v>1</v>
-      </c>
-      <c r="E12" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="1">
-        <v>1</v>
-      </c>
-      <c r="C13" s="1">
-        <v>0</v>
-      </c>
-      <c r="D13" s="1">
-        <v>0</v>
-      </c>
-      <c r="E13" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="1">
-        <v>1</v>
-      </c>
-      <c r="C14" s="1">
-        <v>0</v>
-      </c>
-      <c r="D14" s="1">
-        <v>0</v>
-      </c>
-      <c r="E14" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="B15" s="1">
         <v>1</v>
       </c>
       <c r="C15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="1">
-        <v>1</v>
-      </c>
-      <c r="C16" s="1">
-        <v>0</v>
-      </c>
-      <c r="D16" s="1">
-        <v>0</v>
-      </c>
-      <c r="E16" s="1">
         <v>1</v>
       </c>
     </row>

--- a/data/pricing_plan.xlsx
+++ b/data/pricing_plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yangfan/project/lobeai/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98391938-93FA-4A4F-9B7C-FB055572DF65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AFA6F16-3714-4443-B39C-129BDF8E5387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,15 +41,6 @@
     <t>free</t>
   </si>
   <si>
-    <t>basic</t>
-  </si>
-  <si>
-    <t>pro</t>
-  </si>
-  <si>
-    <t>enterprise</t>
-  </si>
-  <si>
     <t>anthropic/claude-haiku-4.5</t>
   </si>
   <si>
@@ -90,6 +81,18 @@
   </si>
   <si>
     <t>google/gemini-3-pro-preview</t>
+  </si>
+  <si>
+    <t>default</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vip</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>svip</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -495,18 +498,18 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:7 16384:16384">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
@@ -525,7 +528,7 @@
     </row>
     <row r="3" spans="1:7 16384:16384">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
@@ -544,7 +547,7 @@
     </row>
     <row r="4" spans="1:7 16384:16384">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
@@ -561,7 +564,7 @@
     </row>
     <row r="5" spans="1:7 16384:16384">
       <c r="A5" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
@@ -582,7 +585,7 @@
     </row>
     <row r="6" spans="1:7 16384:16384">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
@@ -599,7 +602,7 @@
     </row>
     <row r="7" spans="1:7 16384:16384">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
@@ -616,7 +619,7 @@
     </row>
     <row r="8" spans="1:7 16384:16384">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B8" s="1">
         <v>1</v>
@@ -633,7 +636,7 @@
     </row>
     <row r="9" spans="1:7 16384:16384">
       <c r="A9" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B9" s="1">
         <v>1</v>
@@ -650,7 +653,7 @@
     </row>
     <row r="10" spans="1:7 16384:16384">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B10" s="1">
         <v>1</v>
@@ -667,7 +670,7 @@
     </row>
     <row r="11" spans="1:7 16384:16384">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B11" s="1">
         <v>1</v>
@@ -684,7 +687,7 @@
     </row>
     <row r="12" spans="1:7 16384:16384">
       <c r="A12" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B12" s="1">
         <v>1</v>
@@ -701,7 +704,7 @@
     </row>
     <row r="13" spans="1:7 16384:16384">
       <c r="A13" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B13" s="1">
         <v>1</v>
@@ -718,7 +721,7 @@
     </row>
     <row r="14" spans="1:7 16384:16384">
       <c r="A14" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1">
         <v>1</v>
@@ -735,7 +738,7 @@
     </row>
     <row r="15" spans="1:7 16384:16384">
       <c r="A15" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B15" s="1">
         <v>1</v>
